--- a/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:15:22+00:00</t>
+    <t>2025-07-07T09:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:23:07+00:00</t>
+    <t>2025-07-07T09:24:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:24:06+00:00</t>
+    <t>2025-07-07T15:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
